--- a/testdata/realdata/services.xlsx
+++ b/testdata/realdata/services.xlsx
@@ -486,7 +486,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -597,7 +597,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>停用</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>开通</t>
+          <t>在网</t>
         </is>
       </c>
     </row>

--- a/testdata/realdata/services.xlsx
+++ b/testdata/realdata/services.xlsx
@@ -476,7 +476,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>DEV-244077958-01</t>
+          <t>DEV-1727803072-01</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>DEV-244081515-01</t>
+          <t>DEV-1933473774-01</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -550,7 +550,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>DEV-1727803072-01</t>
+          <t>DEV-2168737545-01</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -587,7 +587,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>DEV-469656125-01</t>
+          <t>DEV-2289935762-01</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>DEV-678337697-01</t>
+          <t>DEV-244076868-01</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>DEV-962010355-01</t>
+          <t>DEV-244076933-01</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>DEV-280162986-01</t>
+          <t>DEV-244077958-01</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>DEV-4059698545-01</t>
+          <t>DEV-244079035-01</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
